--- a/data/trans_dic/P1401-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P1401-Habitat-trans_dic.xlsx
@@ -635,7 +635,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,15%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,44; 2,0</t>
+          <t>0,44; 2,09</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,28; 1,76</t>
+          <t>0,36; 2,1</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,07; 2,82</t>
+          <t>1,13; 2,86</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,9; 2,89</t>
+          <t>0,9; 2,91</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,39; 3,93</t>
+          <t>1,45; 3,9</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,69; 3,39</t>
+          <t>1,72; 3,4</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,85; 2,02</t>
+          <t>0,82; 2,11</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,05; 2,53</t>
+          <t>1,03; 2,49</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,54; 2,78</t>
+          <t>1,66; 2,8</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,12%</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,31; 1,7</t>
+          <t>0,32; 1,65</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,37; 1,47</t>
+          <t>0,37; 1,5</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,75; 2,62</t>
+          <t>1,3; 2,94</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,13; 2,91</t>
+          <t>1,07; 3,0</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,83; 2,44</t>
+          <t>0,91; 2,66</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,72; 3,21</t>
+          <t>1,61; 3,01</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,87; 1,91</t>
+          <t>0,89; 2,0</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,7; 1,72</t>
+          <t>0,7; 1,68</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,31; 2,63</t>
+          <t>1,66; 2,77</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,71%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,39; 1,84</t>
+          <t>0,39; 1,93</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,23; 1,49</t>
+          <t>0,23; 1,28</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,18; 3,14</t>
+          <t>1,24; 3,17</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,92; 3,09</t>
+          <t>0,89; 3,05</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,68; 2,44</t>
+          <t>0,62; 2,53</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,51; 1,9</t>
+          <t>0,95; 2,3</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,75; 2,01</t>
+          <t>0,79; 2,15</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,57; 1,53</t>
+          <t>0,56; 1,54</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,95; 2,23</t>
+          <t>1,18; 2,47</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,67%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,07; 2,9</t>
+          <t>1,04; 2,91</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,63; 2,07</t>
+          <t>0,64; 2,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,71; 3,62</t>
+          <t>1,72; 3,5</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,66; 3,91</t>
+          <t>1,64; 3,92</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,87; 4,09</t>
+          <t>1,87; 4,04</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,9; 3,48</t>
+          <t>2,16; 3,6</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,66; 3,02</t>
+          <t>1,62; 2,95</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,47; 2,8</t>
+          <t>1,43; 2,82</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,04; 3,18</t>
+          <t>2,12; 3,27</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,2%</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,8; 1,55</t>
+          <t>0,84; 1,6</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,59; 1,22</t>
+          <t>0,62; 1,25</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,53; 2,48</t>
+          <t>1,65; 2,57</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,58; 2,64</t>
+          <t>1,54; 2,5</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,55; 2,67</t>
+          <t>1,51; 2,55</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,66; 2,55</t>
+          <t>1,91; 2,63</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,29; 1,94</t>
+          <t>1,31; 1,92</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,19; 1,76</t>
+          <t>1,2; 1,78</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,74; 2,4</t>
+          <t>1,94; 2,5</t>
         </is>
       </c>
     </row>
@@ -1374,7 +1374,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11313</t>
+          <t>12753</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16262</t>
+          <t>17901</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>27575</t>
+          <t>30654</t>
         </is>
       </c>
     </row>
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3113; 14083</t>
+          <t>3072; 14671</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1866; 11867</t>
+          <t>2457; 14170</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6811; 17907</t>
+          <t>7775; 19788</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6243; 20154</t>
+          <t>6248; 20304</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>9321; 26439</t>
+          <t>9786; 26272</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11432; 22886</t>
+          <t>12629; 24944</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11883; 28241</t>
+          <t>11414; 29516</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>14106; 34160</t>
+          <t>13837; 33612</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>20207; 36498</t>
+          <t>23570; 39797</t>
         </is>
       </c>
     </row>
@@ -1537,7 +1537,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>20272</t>
+          <t>21150</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>22305</t>
+          <t>23736</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>42577</t>
+          <t>44886</t>
         </is>
       </c>
     </row>
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3178; 17314</t>
+          <t>3220; 16761</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3807; 15053</t>
+          <t>3780; 15377</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9001; 31229</t>
+          <t>13616; 30877</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11610; 29964</t>
+          <t>10985; 30903</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8655; 25420</t>
+          <t>9478; 27745</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>16432; 30748</t>
+          <t>17257; 32209</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>17848; 39123</t>
+          <t>18160; 40936</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>14446; 35506</t>
+          <t>14497; 34781</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>28215; 56523</t>
+          <t>35243; 58740</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14129</t>
+          <t>15501</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1715,7 +1715,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10914</t>
+          <t>12000</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1730,7 +1730,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>25043</t>
+          <t>27501</t>
         </is>
       </c>
     </row>
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2922; 13947</t>
+          <t>2957; 14611</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1770; 11290</t>
+          <t>1730; 9757</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8268; 21970</t>
+          <t>9871; 25276</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7145; 24035</t>
+          <t>6926; 23703</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>5363; 19182</t>
+          <t>4863; 19846</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4756; 17702</t>
+          <t>7686; 18594</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11557; 30840</t>
+          <t>12114; 33048</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>8756; 23636</t>
+          <t>8686; 23844</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>15442; 36296</t>
+          <t>18969; 39733</t>
         </is>
       </c>
     </row>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>23164</t>
+          <t>25103</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1878,7 +1878,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>28458</t>
+          <t>31181</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>51622</t>
+          <t>56284</t>
         </is>
       </c>
     </row>
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>10174; 27508</t>
+          <t>9898; 27535</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5886; 19382</t>
+          <t>5960; 18707</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>15805; 33529</t>
+          <t>17011; 34521</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>17455; 41092</t>
+          <t>17254; 41190</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>19545; 42647</t>
+          <t>19544; 42161</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>20711; 38018</t>
+          <t>24092; 40222</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>33194; 60299</t>
+          <t>32340; 58972</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>29145; 55392</t>
+          <t>28422; 55790</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>41048; 64073</t>
+          <t>44689; 68907</t>
         </is>
       </c>
     </row>
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>68877</t>
+          <t>74507</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>77940</t>
+          <t>84818</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2056,7 +2056,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>146817</t>
+          <t>159325</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>27339; 53228</t>
+          <t>28645; 54935</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>20040; 41430</t>
+          <t>21201; 42386</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>52962; 85695</t>
+          <t>58261; 90426</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>56327; 93964</t>
+          <t>54850; 88816</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>55106; 94528</t>
+          <t>53433; 90386</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>60692; 93196</t>
+          <t>71138; 98188</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>89974; 135408</t>
+          <t>91287; 134369</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>82250; 122264</t>
+          <t>82952; 123352</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>123640; 170753</t>
+          <t>140385; 181701</t>
         </is>
       </c>
     </row>
